--- a/out/thesis/models/regression_diagnostics.xlsx
+++ b/out/thesis/models/regression_diagnostics.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>model</t>
   </si>
@@ -52,34 +52,16 @@
     <t>completion_car</t>
   </si>
   <si>
-    <t>announcement_bhar</t>
-  </si>
-  <si>
-    <t>completion_bhar</t>
-  </si>
-  <si>
     <t>CAR_ANN_1_1</t>
   </si>
   <si>
     <t>CAR_CLOSE_1_1</t>
   </si>
   <si>
-    <t>BHAR_ANN_120</t>
-  </si>
-  <si>
-    <t>BHAR_CLOSE_120</t>
-  </si>
-  <si>
     <t>ANN_LIQUIDITY_60D, ANN_VOLATILITY_60D, stake_pct_std, deal_value_usd_mn_std, C(deal_status_clean)</t>
   </si>
   <si>
     <t>CLOSE_LIQUIDITY_60D, CLOSE_VOLATILITY_60D, stake_pct_std, CLOSE_ROE, CLOSE_P_B, CLOSE_P_E, CLOSE_TOTAL_ASSETS, CLOSE_MARKET_CAP, C(deal_status_clean)</t>
-  </si>
-  <si>
-    <t>stake_pct_std, ANN_LIQUIDITY_60D, ANN_VOLATILITY_60D, deal_value_usd_mn_std, C(deal_status_clean)</t>
-  </si>
-  <si>
-    <t>stake_pct_std, CLOSE_LIQUIDITY_60D, CLOSE_VOLATILITY_60D, CLOSE_ROE, CLOSE_P_B, CLOSE_P_E, CLOSE_TOTAL_ASSETS, CLOSE_MARKET_CAP, C(deal_status_clean)</t>
   </si>
 </sst>
 </file>
@@ -411,7 +393,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:10">
@@ -451,31 +433,31 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C2">
         <v>66</v>
       </c>
       <c r="D2">
-        <v>0.0001989583144299534</v>
+        <v>0.0007999050837516064</v>
       </c>
       <c r="E2">
-        <v>-228.8343962348716</v>
+        <v>-229.438604727234</v>
       </c>
       <c r="F2">
-        <v>-211.3171582986602</v>
+        <v>-211.9213667910225</v>
       </c>
       <c r="G2">
-        <v>1.4856676194873E-09</v>
+        <v>1.422851611923113E-09</v>
       </c>
       <c r="H2">
-        <v>1.673276531130177</v>
+        <v>1.669406338012255</v>
       </c>
       <c r="I2">
-        <v>0.1079526986040431</v>
+        <v>0.09727634598314629</v>
       </c>
       <c r="J2" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -483,95 +465,31 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3">
+        <v>52</v>
+      </c>
+      <c r="D3">
+        <v>0.1629842427406559</v>
+      </c>
+      <c r="E3">
+        <v>-229.1052989176625</v>
+      </c>
+      <c r="F3">
+        <v>-207.6416180132668</v>
+      </c>
+      <c r="G3">
+        <v>4.966337278673077E-05</v>
+      </c>
+      <c r="H3">
+        <v>2.108845695216705</v>
+      </c>
+      <c r="I3">
+        <v>0.7587884502846137</v>
+      </c>
+      <c r="J3" t="s">
         <v>15</v>
-      </c>
-      <c r="C3">
-        <v>53</v>
-      </c>
-      <c r="D3">
-        <v>0.1997773026788447</v>
-      </c>
-      <c r="E3">
-        <v>-231.8629848087437</v>
-      </c>
-      <c r="F3">
-        <v>-208.2194818461182</v>
-      </c>
-      <c r="G3">
-        <v>1.066212245018238E-19</v>
-      </c>
-      <c r="H3">
-        <v>2.160082492664714</v>
-      </c>
-      <c r="I3">
-        <v>0.8467990627788098</v>
-      </c>
-      <c r="J3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" t="s">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4">
-        <v>66</v>
-      </c>
-      <c r="D4">
-        <v>0.09486963459316611</v>
-      </c>
-      <c r="E4">
-        <v>-42.1228094167501</v>
-      </c>
-      <c r="F4">
-        <v>-24.6055714805387</v>
-      </c>
-      <c r="G4">
-        <v>2.979011655449283E-08</v>
-      </c>
-      <c r="H4">
-        <v>1.888908308795977</v>
-      </c>
-      <c r="I4">
-        <v>0.51827338036521</v>
-      </c>
-      <c r="J4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5">
-        <v>50</v>
-      </c>
-      <c r="D5">
-        <v>-0.006214966518821363</v>
-      </c>
-      <c r="E5">
-        <v>8.17704872704708</v>
-      </c>
-      <c r="F5">
-        <v>31.12132479218483</v>
-      </c>
-      <c r="G5">
-        <v>1.862874605391663E-06</v>
-      </c>
-      <c r="H5">
-        <v>0.9116150434353768</v>
-      </c>
-      <c r="I5">
-        <v>0.05301266435541624</v>
-      </c>
-      <c r="J5" t="s">
-        <v>21</v>
       </c>
     </row>
   </sheetData>

--- a/out/thesis/models/regression_diagnostics.xlsx
+++ b/out/thesis/models/regression_diagnostics.xlsx
@@ -61,7 +61,7 @@
     <t>ANN_LIQUIDITY_60D, ANN_VOLATILITY_60D, stake_pct_std, deal_value_usd_mn_std, C(deal_status_clean)</t>
   </si>
   <si>
-    <t>CLOSE_LIQUIDITY_60D, CLOSE_VOLATILITY_60D, stake_pct_std, CLOSE_ROE, CLOSE_P_B, CLOSE_P_E, CLOSE_TOTAL_ASSETS, CLOSE_MARKET_CAP, C(deal_status_clean)</t>
+    <t>CLOSE_LIQUIDITY_60D, CLOSE_VOLATILITY_60D, stake_pct_std, deal_value_usd_mn_std, C(deal_status_clean)</t>
   </si>
 </sst>
 </file>
@@ -471,22 +471,22 @@
         <v>52</v>
       </c>
       <c r="D3">
-        <v>0.1629842427406559</v>
+        <v>-0.03160606734125149</v>
       </c>
       <c r="E3">
-        <v>-229.1052989176625</v>
+        <v>-185.8526911651583</v>
       </c>
       <c r="F3">
-        <v>-207.6416180132668</v>
+        <v>-172.1939851350883</v>
       </c>
       <c r="G3">
-        <v>4.966337278673077E-05</v>
+        <v>8.942230052591289E-11</v>
       </c>
       <c r="H3">
-        <v>2.108845695216705</v>
+        <v>1.552817839904385</v>
       </c>
       <c r="I3">
-        <v>0.7587884502846137</v>
+        <v>0.953031916032844</v>
       </c>
       <c r="J3" t="s">
         <v>15</v>
